--- a/artfynd/A 24359-2025 artfynd.xlsx
+++ b/artfynd/A 24359-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1361,6 +1361,132 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125378198</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56714</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>609159</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6983178</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24359-2025 artfynd.xlsx
+++ b/artfynd/A 24359-2025 artfynd.xlsx
@@ -1366,7 +1366,7 @@
         <v>125378198</v>
       </c>
       <c r="B8" t="n">
-        <v>56714</v>
+        <v>56828</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 24359-2025 artfynd.xlsx
+++ b/artfynd/A 24359-2025 artfynd.xlsx
@@ -1366,12 +1366,7 @@
         <v>125378198</v>
       </c>
       <c r="B8" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56834</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
